--- a/outputs/RCM.xlsx
+++ b/outputs/RCM.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RCM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RCM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RCM'!$A$6:$P$15</definedName>
@@ -574,7 +574,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
